--- a/resources/HAM_FIYATLAR.xlsx
+++ b/resources/HAM_FIYATLAR.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" tabRatio="963" firstSheet="40" activeTab="46"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" tabRatio="963" firstSheet="44" activeTab="59"/>
   </bookViews>
   <sheets>
     <sheet name="MNZ_TEKSIRA" sheetId="1" r:id="rId1"/>
@@ -64,6 +64,9 @@
     <sheet name="KPK_KONT" sheetId="55" r:id="rId55"/>
     <sheet name="KPK_KAPETMNZKONT" sheetId="56" r:id="rId56"/>
     <sheet name="KPK_LINMNZKONT" sheetId="57" r:id="rId57"/>
+    <sheet name="BOX_WH" sheetId="58" r:id="rId58"/>
+    <sheet name="BOX_LS" sheetId="59" r:id="rId59"/>
+    <sheet name="BOX_STR" sheetId="60" r:id="rId60"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -75,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="73">
   <si>
     <t>W/H</t>
   </si>
@@ -265,6 +268,36 @@
   <si>
     <t>Ø100</t>
   </si>
+  <si>
+    <t>W X H</t>
+  </si>
+  <si>
+    <t>A X A</t>
+  </si>
+  <si>
+    <t>150*150</t>
+  </si>
+  <si>
+    <t>225*225</t>
+  </si>
+  <si>
+    <t>300*300</t>
+  </si>
+  <si>
+    <t>375*375</t>
+  </si>
+  <si>
+    <t>450*450</t>
+  </si>
+  <si>
+    <t>600*600</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>525*525</t>
+  </si>
 </sst>
 </file>
 
@@ -339,7 +372,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -589,11 +622,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -718,6 +766,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -23903,6 +23956,1169 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="46" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="11">
+        <v>100</v>
+      </c>
+      <c r="C1" s="12">
+        <v>150</v>
+      </c>
+      <c r="D1" s="12">
+        <v>200</v>
+      </c>
+      <c r="E1" s="12">
+        <v>250</v>
+      </c>
+      <c r="F1" s="12">
+        <v>300</v>
+      </c>
+      <c r="G1" s="12">
+        <v>350</v>
+      </c>
+      <c r="H1" s="13">
+        <v>400</v>
+      </c>
+      <c r="I1" s="13">
+        <v>450</v>
+      </c>
+      <c r="J1" s="13">
+        <v>500</v>
+      </c>
+      <c r="K1" s="13">
+        <v>600</v>
+      </c>
+      <c r="L1" s="13">
+        <v>700</v>
+      </c>
+      <c r="M1" s="13">
+        <v>800</v>
+      </c>
+      <c r="N1" s="13">
+        <v>900</v>
+      </c>
+      <c r="O1" s="14">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A2" s="15">
+        <v>100</v>
+      </c>
+      <c r="B2" s="19">
+        <v>225</v>
+      </c>
+      <c r="C2" s="19">
+        <v>250</v>
+      </c>
+      <c r="D2" s="19">
+        <v>275</v>
+      </c>
+      <c r="E2" s="19">
+        <v>300</v>
+      </c>
+      <c r="F2" s="19">
+        <v>325</v>
+      </c>
+      <c r="G2" s="19">
+        <v>350</v>
+      </c>
+      <c r="H2" s="19">
+        <v>425</v>
+      </c>
+      <c r="I2" s="19">
+        <v>450</v>
+      </c>
+      <c r="J2" s="19">
+        <v>500</v>
+      </c>
+      <c r="K2" s="19">
+        <v>575</v>
+      </c>
+      <c r="L2" s="19">
+        <v>775</v>
+      </c>
+      <c r="M2" s="19">
+        <v>950</v>
+      </c>
+      <c r="N2" s="19">
+        <v>1125</v>
+      </c>
+      <c r="O2" s="19">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3" s="15">
+        <v>150</v>
+      </c>
+      <c r="B3" s="19">
+        <v>250</v>
+      </c>
+      <c r="C3" s="19">
+        <v>275</v>
+      </c>
+      <c r="D3" s="19">
+        <v>300</v>
+      </c>
+      <c r="E3" s="19">
+        <v>325</v>
+      </c>
+      <c r="F3" s="19">
+        <v>350</v>
+      </c>
+      <c r="G3" s="19">
+        <v>400</v>
+      </c>
+      <c r="H3" s="19">
+        <v>450</v>
+      </c>
+      <c r="I3" s="19">
+        <v>500</v>
+      </c>
+      <c r="J3" s="19">
+        <v>550</v>
+      </c>
+      <c r="K3" s="19">
+        <v>650</v>
+      </c>
+      <c r="L3" s="19">
+        <v>875</v>
+      </c>
+      <c r="M3" s="19">
+        <v>1100</v>
+      </c>
+      <c r="N3" s="19">
+        <v>1300</v>
+      </c>
+      <c r="O3" s="19">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4" s="15">
+        <v>200</v>
+      </c>
+      <c r="B4" s="19">
+        <v>275</v>
+      </c>
+      <c r="C4" s="19">
+        <v>300</v>
+      </c>
+      <c r="D4" s="19">
+        <v>325</v>
+      </c>
+      <c r="E4" s="19">
+        <v>350</v>
+      </c>
+      <c r="F4" s="19">
+        <v>400</v>
+      </c>
+      <c r="G4" s="19">
+        <v>450</v>
+      </c>
+      <c r="H4" s="19">
+        <v>500</v>
+      </c>
+      <c r="I4" s="19">
+        <v>550</v>
+      </c>
+      <c r="J4" s="19">
+        <v>625</v>
+      </c>
+      <c r="K4" s="19">
+        <v>750</v>
+      </c>
+      <c r="L4" s="19">
+        <v>975</v>
+      </c>
+      <c r="M4" s="19">
+        <v>1200</v>
+      </c>
+      <c r="N4" s="19">
+        <v>1450</v>
+      </c>
+      <c r="O4" s="19">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A5" s="15">
+        <v>250</v>
+      </c>
+      <c r="B5" s="19">
+        <v>300</v>
+      </c>
+      <c r="C5" s="19">
+        <v>325</v>
+      </c>
+      <c r="D5" s="19">
+        <v>350</v>
+      </c>
+      <c r="E5" s="19">
+        <v>375</v>
+      </c>
+      <c r="F5" s="19">
+        <v>425</v>
+      </c>
+      <c r="G5" s="19">
+        <v>500</v>
+      </c>
+      <c r="H5" s="19">
+        <v>550</v>
+      </c>
+      <c r="I5" s="19">
+        <v>625</v>
+      </c>
+      <c r="J5" s="19">
+        <v>700</v>
+      </c>
+      <c r="K5" s="19">
+        <v>800</v>
+      </c>
+      <c r="L5" s="19">
+        <v>1075</v>
+      </c>
+      <c r="M5" s="19">
+        <v>1325</v>
+      </c>
+      <c r="N5" s="19">
+        <v>1575</v>
+      </c>
+      <c r="O5" s="19">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6" s="15">
+        <v>300</v>
+      </c>
+      <c r="B6" s="19">
+        <v>325</v>
+      </c>
+      <c r="C6" s="19">
+        <v>350</v>
+      </c>
+      <c r="D6" s="19">
+        <v>375</v>
+      </c>
+      <c r="E6" s="19">
+        <v>400</v>
+      </c>
+      <c r="F6" s="19">
+        <v>475</v>
+      </c>
+      <c r="G6" s="19">
+        <v>550</v>
+      </c>
+      <c r="H6" s="19">
+        <v>600</v>
+      </c>
+      <c r="I6" s="19">
+        <v>650</v>
+      </c>
+      <c r="J6" s="19">
+        <v>725</v>
+      </c>
+      <c r="K6" s="19">
+        <v>875</v>
+      </c>
+      <c r="L6" s="19">
+        <v>1150</v>
+      </c>
+      <c r="M6" s="19">
+        <v>1425</v>
+      </c>
+      <c r="N6" s="19">
+        <v>1700</v>
+      </c>
+      <c r="O6" s="19">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7" s="15">
+        <v>350</v>
+      </c>
+      <c r="B7" s="19">
+        <v>350</v>
+      </c>
+      <c r="C7" s="19">
+        <v>375</v>
+      </c>
+      <c r="D7" s="19">
+        <v>400</v>
+      </c>
+      <c r="E7" s="19">
+        <v>425</v>
+      </c>
+      <c r="F7" s="19">
+        <v>500</v>
+      </c>
+      <c r="G7" s="19">
+        <v>575</v>
+      </c>
+      <c r="H7" s="19">
+        <v>650</v>
+      </c>
+      <c r="I7" s="19">
+        <v>725</v>
+      </c>
+      <c r="J7" s="19">
+        <v>800</v>
+      </c>
+      <c r="K7" s="19">
+        <v>950</v>
+      </c>
+      <c r="L7" s="19">
+        <v>1250</v>
+      </c>
+      <c r="M7" s="19">
+        <v>1550</v>
+      </c>
+      <c r="N7" s="19">
+        <v>1825</v>
+      </c>
+      <c r="O7" s="19">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A8" s="15">
+        <v>400</v>
+      </c>
+      <c r="B8" s="19">
+        <v>375</v>
+      </c>
+      <c r="C8" s="19">
+        <v>400</v>
+      </c>
+      <c r="D8" s="19">
+        <v>425</v>
+      </c>
+      <c r="E8" s="19">
+        <v>475</v>
+      </c>
+      <c r="F8" s="19">
+        <v>550</v>
+      </c>
+      <c r="G8" s="19">
+        <v>650</v>
+      </c>
+      <c r="H8" s="19">
+        <v>725</v>
+      </c>
+      <c r="I8" s="19">
+        <v>800</v>
+      </c>
+      <c r="J8" s="19">
+        <v>900</v>
+      </c>
+      <c r="K8" s="19">
+        <v>1100</v>
+      </c>
+      <c r="L8" s="19">
+        <v>1425</v>
+      </c>
+      <c r="M8" s="19">
+        <v>1775</v>
+      </c>
+      <c r="N8" s="19">
+        <v>2100</v>
+      </c>
+      <c r="O8" s="19">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A9" s="15">
+        <v>450</v>
+      </c>
+      <c r="B9" s="19">
+        <v>400</v>
+      </c>
+      <c r="C9" s="19">
+        <v>425</v>
+      </c>
+      <c r="D9" s="19">
+        <v>450</v>
+      </c>
+      <c r="E9" s="19">
+        <v>525</v>
+      </c>
+      <c r="F9" s="19">
+        <v>650</v>
+      </c>
+      <c r="G9" s="19">
+        <v>725</v>
+      </c>
+      <c r="H9" s="19">
+        <v>800</v>
+      </c>
+      <c r="I9" s="19">
+        <v>925</v>
+      </c>
+      <c r="J9" s="19">
+        <v>1025</v>
+      </c>
+      <c r="K9" s="19">
+        <v>1200</v>
+      </c>
+      <c r="L9" s="19">
+        <v>1600</v>
+      </c>
+      <c r="M9" s="19">
+        <v>1975</v>
+      </c>
+      <c r="N9" s="19">
+        <v>2400</v>
+      </c>
+      <c r="O9" s="19">
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10" s="15">
+        <v>500</v>
+      </c>
+      <c r="B10" s="19">
+        <v>425</v>
+      </c>
+      <c r="C10" s="19">
+        <v>450</v>
+      </c>
+      <c r="D10" s="19">
+        <v>525</v>
+      </c>
+      <c r="E10" s="19">
+        <v>600</v>
+      </c>
+      <c r="F10" s="19">
+        <v>700</v>
+      </c>
+      <c r="G10" s="19">
+        <v>800</v>
+      </c>
+      <c r="H10" s="19">
+        <v>900</v>
+      </c>
+      <c r="I10" s="19">
+        <v>1000</v>
+      </c>
+      <c r="J10" s="19">
+        <v>1125</v>
+      </c>
+      <c r="K10" s="19">
+        <v>1350</v>
+      </c>
+      <c r="L10" s="19">
+        <v>1750</v>
+      </c>
+      <c r="M10" s="19">
+        <v>2200</v>
+      </c>
+      <c r="N10" s="19">
+        <v>2625</v>
+      </c>
+      <c r="O10" s="19">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A11" s="15">
+        <v>600</v>
+      </c>
+      <c r="B11" s="19">
+        <v>450</v>
+      </c>
+      <c r="C11" s="19">
+        <v>475</v>
+      </c>
+      <c r="D11" s="19">
+        <v>550</v>
+      </c>
+      <c r="E11" s="19">
+        <v>650</v>
+      </c>
+      <c r="F11" s="19">
+        <v>750</v>
+      </c>
+      <c r="G11" s="19">
+        <v>850</v>
+      </c>
+      <c r="H11" s="19">
+        <v>975</v>
+      </c>
+      <c r="I11" s="19">
+        <v>1100</v>
+      </c>
+      <c r="J11" s="19">
+        <v>1225</v>
+      </c>
+      <c r="K11" s="19">
+        <v>1450</v>
+      </c>
+      <c r="L11" s="19">
+        <v>1925</v>
+      </c>
+      <c r="M11" s="19">
+        <v>2400</v>
+      </c>
+      <c r="N11" s="19">
+        <v>2850</v>
+      </c>
+      <c r="O11" s="19">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A12" s="15">
+        <v>700</v>
+      </c>
+      <c r="B12" s="19">
+        <v>475</v>
+      </c>
+      <c r="C12" s="19">
+        <v>500</v>
+      </c>
+      <c r="D12" s="19">
+        <v>575</v>
+      </c>
+      <c r="E12" s="19">
+        <v>700</v>
+      </c>
+      <c r="F12" s="19">
+        <v>800</v>
+      </c>
+      <c r="G12" s="19">
+        <v>950</v>
+      </c>
+      <c r="H12" s="19">
+        <v>1050</v>
+      </c>
+      <c r="I12" s="19">
+        <v>1200</v>
+      </c>
+      <c r="J12" s="19">
+        <v>1300</v>
+      </c>
+      <c r="K12" s="19">
+        <v>1550</v>
+      </c>
+      <c r="L12" s="19">
+        <v>2050</v>
+      </c>
+      <c r="M12" s="19">
+        <v>2550</v>
+      </c>
+      <c r="N12" s="19">
+        <v>3050</v>
+      </c>
+      <c r="O12" s="19">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A13" s="15">
+        <v>800</v>
+      </c>
+      <c r="B13" s="19">
+        <v>500</v>
+      </c>
+      <c r="C13" s="19">
+        <v>550</v>
+      </c>
+      <c r="D13" s="19">
+        <v>650</v>
+      </c>
+      <c r="E13" s="19">
+        <v>800</v>
+      </c>
+      <c r="F13" s="19">
+        <v>950</v>
+      </c>
+      <c r="G13" s="19">
+        <v>1075</v>
+      </c>
+      <c r="H13" s="19">
+        <v>1200</v>
+      </c>
+      <c r="I13" s="19">
+        <v>1375</v>
+      </c>
+      <c r="J13" s="19">
+        <v>1500</v>
+      </c>
+      <c r="K13" s="19">
+        <v>1800</v>
+      </c>
+      <c r="L13" s="19">
+        <v>2400</v>
+      </c>
+      <c r="M13" s="19">
+        <v>2975</v>
+      </c>
+      <c r="N13" s="19">
+        <v>3550</v>
+      </c>
+      <c r="O13" s="19">
+        <v>4725</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A14" s="15">
+        <v>900</v>
+      </c>
+      <c r="B14" s="19">
+        <v>525</v>
+      </c>
+      <c r="C14" s="19">
+        <v>600</v>
+      </c>
+      <c r="D14" s="19">
+        <v>750</v>
+      </c>
+      <c r="E14" s="19">
+        <v>900</v>
+      </c>
+      <c r="F14" s="19">
+        <v>1050</v>
+      </c>
+      <c r="G14" s="19">
+        <v>1200</v>
+      </c>
+      <c r="H14" s="19">
+        <v>1350</v>
+      </c>
+      <c r="I14" s="19">
+        <v>1550</v>
+      </c>
+      <c r="J14" s="19">
+        <v>1700</v>
+      </c>
+      <c r="K14" s="19">
+        <v>2000</v>
+      </c>
+      <c r="L14" s="19">
+        <v>2700</v>
+      </c>
+      <c r="M14" s="19">
+        <v>3300</v>
+      </c>
+      <c r="N14" s="19">
+        <v>4000</v>
+      </c>
+      <c r="O14" s="19">
+        <v>5300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A15" s="15">
+        <v>1000</v>
+      </c>
+      <c r="B15" s="19">
+        <v>550</v>
+      </c>
+      <c r="C15" s="19">
+        <v>650</v>
+      </c>
+      <c r="D15" s="19">
+        <v>800</v>
+      </c>
+      <c r="E15" s="19">
+        <v>975</v>
+      </c>
+      <c r="F15" s="19">
+        <v>1150</v>
+      </c>
+      <c r="G15" s="19">
+        <v>1350</v>
+      </c>
+      <c r="H15" s="19">
+        <v>1500</v>
+      </c>
+      <c r="I15" s="19">
+        <v>1700</v>
+      </c>
+      <c r="J15" s="19">
+        <v>1875</v>
+      </c>
+      <c r="K15" s="19">
+        <v>2250</v>
+      </c>
+      <c r="L15" s="19">
+        <v>2950</v>
+      </c>
+      <c r="M15" s="19">
+        <v>3675</v>
+      </c>
+      <c r="N15" s="19">
+        <v>4425</v>
+      </c>
+      <c r="O15" s="19">
+        <v>5875</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="16">
+        <v>1100</v>
+      </c>
+      <c r="B16" s="19">
+        <v>600</v>
+      </c>
+      <c r="C16" s="19">
+        <v>700</v>
+      </c>
+      <c r="D16" s="19">
+        <v>900</v>
+      </c>
+      <c r="E16" s="19">
+        <v>1075</v>
+      </c>
+      <c r="F16" s="19">
+        <v>1250</v>
+      </c>
+      <c r="G16" s="19">
+        <v>1450</v>
+      </c>
+      <c r="H16" s="19">
+        <v>1650</v>
+      </c>
+      <c r="I16" s="19">
+        <v>1850</v>
+      </c>
+      <c r="J16" s="19">
+        <v>2050</v>
+      </c>
+      <c r="K16" s="19">
+        <v>2450</v>
+      </c>
+      <c r="L16" s="19">
+        <v>3200</v>
+      </c>
+      <c r="M16" s="19">
+        <v>4000</v>
+      </c>
+      <c r="N16" s="19">
+        <v>4800</v>
+      </c>
+      <c r="O16" s="19">
+        <v>6375</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="46" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="11">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12">
+        <v>2</v>
+      </c>
+      <c r="D1" s="12">
+        <v>3</v>
+      </c>
+      <c r="E1" s="12">
+        <v>4</v>
+      </c>
+      <c r="F1" s="12">
+        <v>5</v>
+      </c>
+      <c r="G1" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="15">
+        <v>500</v>
+      </c>
+      <c r="B2" s="19">
+        <v>275</v>
+      </c>
+      <c r="C2" s="19">
+        <v>375</v>
+      </c>
+      <c r="D2" s="19">
+        <v>475</v>
+      </c>
+      <c r="E2" s="19">
+        <v>600</v>
+      </c>
+      <c r="F2" s="19">
+        <v>675</v>
+      </c>
+      <c r="G2" s="19">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="15">
+        <v>600</v>
+      </c>
+      <c r="B3" s="19">
+        <v>300</v>
+      </c>
+      <c r="C3" s="19">
+        <v>450</v>
+      </c>
+      <c r="D3" s="19">
+        <v>575</v>
+      </c>
+      <c r="E3" s="19">
+        <v>725</v>
+      </c>
+      <c r="F3" s="19">
+        <v>775</v>
+      </c>
+      <c r="G3" s="19">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="15">
+        <v>700</v>
+      </c>
+      <c r="B4" s="19">
+        <v>350</v>
+      </c>
+      <c r="C4" s="19">
+        <v>500</v>
+      </c>
+      <c r="D4" s="19">
+        <v>650</v>
+      </c>
+      <c r="E4" s="19">
+        <v>825</v>
+      </c>
+      <c r="F4" s="19">
+        <v>875</v>
+      </c>
+      <c r="G4" s="19">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="15">
+        <v>800</v>
+      </c>
+      <c r="B5" s="19">
+        <v>400</v>
+      </c>
+      <c r="C5" s="19">
+        <v>550</v>
+      </c>
+      <c r="D5" s="19">
+        <v>725</v>
+      </c>
+      <c r="E5" s="19">
+        <v>925</v>
+      </c>
+      <c r="F5" s="19">
+        <v>1000</v>
+      </c>
+      <c r="G5" s="19">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="15">
+        <v>900</v>
+      </c>
+      <c r="B6" s="19">
+        <v>425</v>
+      </c>
+      <c r="C6" s="19">
+        <v>575</v>
+      </c>
+      <c r="D6" s="19">
+        <v>750</v>
+      </c>
+      <c r="E6" s="19">
+        <v>975</v>
+      </c>
+      <c r="F6" s="19">
+        <v>1075</v>
+      </c>
+      <c r="G6" s="19">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="15">
+        <v>1000</v>
+      </c>
+      <c r="B7" s="19">
+        <v>450</v>
+      </c>
+      <c r="C7" s="19">
+        <v>625</v>
+      </c>
+      <c r="D7" s="19">
+        <v>825</v>
+      </c>
+      <c r="E7" s="19">
+        <v>1050</v>
+      </c>
+      <c r="F7" s="19">
+        <v>1175</v>
+      </c>
+      <c r="G7" s="19">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="15">
+        <v>1100</v>
+      </c>
+      <c r="B8" s="19">
+        <v>500</v>
+      </c>
+      <c r="C8" s="19">
+        <v>700</v>
+      </c>
+      <c r="D8" s="19">
+        <v>900</v>
+      </c>
+      <c r="E8" s="19">
+        <v>1125</v>
+      </c>
+      <c r="F8" s="19">
+        <v>1325</v>
+      </c>
+      <c r="G8" s="19">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="15">
+        <v>1200</v>
+      </c>
+      <c r="B9" s="19">
+        <v>525</v>
+      </c>
+      <c r="C9" s="19">
+        <v>750</v>
+      </c>
+      <c r="D9" s="19">
+        <v>975</v>
+      </c>
+      <c r="E9" s="19">
+        <v>1200</v>
+      </c>
+      <c r="F9" s="19">
+        <v>1425</v>
+      </c>
+      <c r="G9" s="19">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="15">
+        <v>1300</v>
+      </c>
+      <c r="B10" s="19">
+        <v>575</v>
+      </c>
+      <c r="C10" s="19">
+        <v>800</v>
+      </c>
+      <c r="D10" s="19">
+        <v>1050</v>
+      </c>
+      <c r="E10" s="19">
+        <v>1300</v>
+      </c>
+      <c r="F10" s="19">
+        <v>1525</v>
+      </c>
+      <c r="G10" s="19">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="15">
+        <v>1400</v>
+      </c>
+      <c r="B11" s="19">
+        <v>600</v>
+      </c>
+      <c r="C11" s="19">
+        <v>850</v>
+      </c>
+      <c r="D11" s="19">
+        <v>1100</v>
+      </c>
+      <c r="E11" s="19">
+        <v>1375</v>
+      </c>
+      <c r="F11" s="19">
+        <v>1650</v>
+      </c>
+      <c r="G11" s="19">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="15">
+        <v>1500</v>
+      </c>
+      <c r="B12" s="19">
+        <v>650</v>
+      </c>
+      <c r="C12" s="19">
+        <v>900</v>
+      </c>
+      <c r="D12" s="19">
+        <v>1175</v>
+      </c>
+      <c r="E12" s="19">
+        <v>1475</v>
+      </c>
+      <c r="F12" s="19">
+        <v>1750</v>
+      </c>
+      <c r="G12" s="19">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="15">
+        <v>1600</v>
+      </c>
+      <c r="B13" s="19">
+        <v>700</v>
+      </c>
+      <c r="C13" s="19">
+        <v>1000</v>
+      </c>
+      <c r="D13" s="19">
+        <v>1275</v>
+      </c>
+      <c r="E13" s="19">
+        <v>1600</v>
+      </c>
+      <c r="F13" s="19">
+        <v>1900</v>
+      </c>
+      <c r="G13" s="19">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="15">
+        <v>1700</v>
+      </c>
+      <c r="B14" s="19">
+        <v>750</v>
+      </c>
+      <c r="C14" s="19">
+        <v>1050</v>
+      </c>
+      <c r="D14" s="19">
+        <v>1350</v>
+      </c>
+      <c r="E14" s="19">
+        <v>1675</v>
+      </c>
+      <c r="F14" s="19">
+        <v>2000</v>
+      </c>
+      <c r="G14" s="19">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="15">
+        <v>1800</v>
+      </c>
+      <c r="B15" s="19">
+        <v>775</v>
+      </c>
+      <c r="C15" s="19">
+        <v>1100</v>
+      </c>
+      <c r="D15" s="19">
+        <v>1425</v>
+      </c>
+      <c r="E15" s="19">
+        <v>1775</v>
+      </c>
+      <c r="F15" s="19">
+        <v>2100</v>
+      </c>
+      <c r="G15" s="19">
+        <v>2425</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="21">
+        <v>1900</v>
+      </c>
+      <c r="B16" s="19">
+        <v>800</v>
+      </c>
+      <c r="C16" s="19">
+        <v>1150</v>
+      </c>
+      <c r="D16" s="19">
+        <v>1500</v>
+      </c>
+      <c r="E16" s="19">
+        <v>1850</v>
+      </c>
+      <c r="F16" s="19">
+        <v>2200</v>
+      </c>
+      <c r="G16" s="19">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="21">
+        <v>2000</v>
+      </c>
+      <c r="B17" s="19">
+        <v>850</v>
+      </c>
+      <c r="C17" s="19">
+        <v>1200</v>
+      </c>
+      <c r="D17" s="19">
+        <v>1575</v>
+      </c>
+      <c r="E17" s="19">
+        <v>1950</v>
+      </c>
+      <c r="F17" s="19">
+        <v>2325</v>
+      </c>
+      <c r="G17" s="19">
+        <v>2675</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O16"/>
@@ -24658,6 +25874,80 @@
       </c>
       <c r="O16" s="1">
         <v>8290</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="47" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="48" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="47" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="48">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="48">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="48">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="48">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="48">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="48">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="48">
+        <v>2000</v>
       </c>
     </row>
   </sheetData>
